--- a/artfynd/A 51246-2024 artfynd.xlsx
+++ b/artfynd/A 51246-2024 artfynd.xlsx
@@ -924,7 +924,7 @@
         <v>121149663</v>
       </c>
       <c r="B4" t="n">
-        <v>91998</v>
+        <v>92008</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 51246-2024 artfynd.xlsx
+++ b/artfynd/A 51246-2024 artfynd.xlsx
@@ -924,7 +924,7 @@
         <v>121149663</v>
       </c>
       <c r="B4" t="n">
-        <v>92008</v>
+        <v>92020</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 51246-2024 artfynd.xlsx
+++ b/artfynd/A 51246-2024 artfynd.xlsx
@@ -924,7 +924,7 @@
         <v>121149663</v>
       </c>
       <c r="B4" t="n">
-        <v>92020</v>
+        <v>92021</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 51246-2024 artfynd.xlsx
+++ b/artfynd/A 51246-2024 artfynd.xlsx
@@ -924,7 +924,7 @@
         <v>121149663</v>
       </c>
       <c r="B4" t="n">
-        <v>92021</v>
+        <v>92024</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 51246-2024 artfynd.xlsx
+++ b/artfynd/A 51246-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1030,6 +1030,107 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126067681</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98258</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Gälkhyttan, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>604858</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6507203</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lars Fredriksson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lars Fredriksson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51246-2024 artfynd.xlsx
+++ b/artfynd/A 51246-2024 artfynd.xlsx
@@ -1035,7 +1035,7 @@
         <v>126067681</v>
       </c>
       <c r="B5" t="n">
-        <v>98258</v>
+        <v>98259</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 51246-2024 artfynd.xlsx
+++ b/artfynd/A 51246-2024 artfynd.xlsx
@@ -1035,7 +1035,7 @@
         <v>126067681</v>
       </c>
       <c r="B5" t="n">
-        <v>98259</v>
+        <v>98261</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 51246-2024 artfynd.xlsx
+++ b/artfynd/A 51246-2024 artfynd.xlsx
@@ -1035,7 +1035,7 @@
         <v>126067681</v>
       </c>
       <c r="B5" t="n">
-        <v>98261</v>
+        <v>98263</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 51246-2024 artfynd.xlsx
+++ b/artfynd/A 51246-2024 artfynd.xlsx
@@ -1035,7 +1035,7 @@
         <v>126067681</v>
       </c>
       <c r="B5" t="n">
-        <v>98263</v>
+        <v>98265</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 51246-2024 artfynd.xlsx
+++ b/artfynd/A 51246-2024 artfynd.xlsx
@@ -1035,7 +1035,7 @@
         <v>126067681</v>
       </c>
       <c r="B5" t="n">
-        <v>98265</v>
+        <v>98269</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 51246-2024 artfynd.xlsx
+++ b/artfynd/A 51246-2024 artfynd.xlsx
@@ -1035,7 +1035,7 @@
         <v>126067681</v>
       </c>
       <c r="B5" t="n">
-        <v>98269</v>
+        <v>98272</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 51246-2024 artfynd.xlsx
+++ b/artfynd/A 51246-2024 artfynd.xlsx
@@ -1035,7 +1035,7 @@
         <v>126067681</v>
       </c>
       <c r="B5" t="n">
-        <v>98272</v>
+        <v>98281</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 51246-2024 artfynd.xlsx
+++ b/artfynd/A 51246-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>83288982</v>
+        <v>121512524</v>
       </c>
       <c r="B2" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220785</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gälkhyttedamman, Srm</t>
+          <t>Gälkhyttedammen, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>604770.2060339827</v>
+        <v>604774</v>
       </c>
       <c r="R2" t="n">
-        <v>6507124.384043958</v>
+        <v>6507087</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,29 +741,14 @@
           <t>Tuna</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>C07C1765-1B82-4D20-81AD-6106DCE8449A</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2005-06-03</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-12-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2005-06-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-12-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,83 +757,71 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Rikard Sellberg</t>
+          <t>Eva Grusell</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Rikard Sellberg</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Trädportalen</t>
-        </is>
-      </c>
+          <t>Eva Grusell</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>95547492</v>
+        <v>121149663</v>
       </c>
       <c r="B3" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223597</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>21</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gälkhyttestugan, Sörmlandsleden, Srm</t>
+          <t>Tuna, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>604870.646344471</v>
+        <v>604687</v>
       </c>
       <c r="R3" t="n">
-        <v>6507224.856837448</v>
+        <v>6507098</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,22 +845,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-08-17</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-08-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,34 +864,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anton Johansson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anton Johansson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121149663</v>
+        <v>95547539</v>
       </c>
       <c r="B4" t="n">
-        <v>92024</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>61491</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -937,41 +893,54 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>106670</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart skogssnigel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Arion ater ater</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>21</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tuna, Srm</t>
+          <t>Stora Bötets naturreservat, Gälkhyttedammen, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604687</v>
+        <v>604716</v>
       </c>
       <c r="R4" t="n">
-        <v>6507098</v>
+        <v>6507066</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -995,17 +964,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2021-08-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2021-08-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,67 +978,68 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anton Johansson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anton Johansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126067681</v>
+        <v>83288982</v>
       </c>
       <c r="B5" t="n">
-        <v>98281</v>
+        <v>106813</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223597</v>
+        <v>220785</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gälkhyttan, Srm</t>
+          <t>Gälkhyttedamman, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>604858</v>
+        <v>604770</v>
       </c>
       <c r="R5" t="n">
-        <v>6507203</v>
+        <v>6507124</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1099,14 +1064,19 @@
           <t>Tuna</t>
         </is>
       </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>C07C1765-1B82-4D20-81AD-6106DCE8449A</t>
+        </is>
+      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2005-06-03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2005-06-03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,15 +1091,226 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Rikard Sellberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Rikard Sellberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>95547492</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Gälkhyttestugan, Sörmlandsleden, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>604871</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6507224</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-08-17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-08-17</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anton Johansson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anton Johansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126067681</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Gälkhyttan, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>604858</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6507203</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Tuna</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Lars Fredriksson</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Lars Fredriksson</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51246-2024 artfynd.xlsx
+++ b/artfynd/A 51246-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121512524</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121149663</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -994,6 +1009,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95547539</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,6 +1124,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83288982</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1210,6 +1235,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95547492</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1311,8 +1341,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126067681</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>